--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:58:08+00:00</t>
+    <t>2026-06-01T14:28:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6110,7 +6110,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>176</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>74</v>
@@ -6514,7 +6514,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>186</v>
       </c>
@@ -6529,13 +6529,13 @@
         <v>62</v>
       </c>
       <c r="F43" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>74</v>
@@ -6617,7 +6617,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" hidden="true">
+    <row r="44">
       <c r="A44" t="s" s="2">
         <v>189</v>
       </c>
@@ -6632,13 +6632,13 @@
         <v>190</v>
       </c>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>75</v>
       </c>
       <c r="H44" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I44" t="s" s="2">
         <v>74</v>
@@ -6926,7 +6926,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>201</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>75</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>74</v>

--- a/nriss-patch-1/ig/StructureDefinition-fr-cda-evaluation.xlsx
+++ b/nriss-patch-1/ig/StructureDefinition-fr-cda-evaluation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T14:28:18+00:00</t>
+    <t>2026-06-01T15:28:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
